--- a/exemple-ePrescription/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/exemple-ePrescription/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T08:51:06+00:00</t>
+    <t>2026-05-06T11:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -12151,7 +12151,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>245</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>74</v>
@@ -12456,7 +12456,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>253</v>
       </c>
@@ -12471,13 +12471,13 @@
         <v>62</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>74</v>
@@ -12559,7 +12559,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>257</v>
       </c>
@@ -12574,13 +12574,13 @@
         <v>258</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>74</v>
@@ -12868,7 +12868,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>271</v>
       </c>
@@ -12889,7 +12889,7 @@
         <v>75</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>74</v>
